--- a/data/gravel/Singular Gryphon steel 2025.xlsx
+++ b/data/gravel/Singular Gryphon steel 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A018FC3-9960-5C44-8D2A-8E9302AE8019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321CE043-3ECD-9640-B68D-880B1A1BDA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25720" yWindow="-18980" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>a8:e35</t>
+  </si>
+  <si>
+    <t>https://singularcycles.com/cdn/shop/files/edited_4.jpg?v=1753953935&amp;width=2200</t>
   </si>
 </sst>
 </file>
@@ -792,6 +795,11 @@
         <v>96</v>
       </c>
     </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
@@ -1416,15 +1424,15 @@
         <v>25</v>
       </c>
       <c r="C30" s="2">
-        <f>3*25.4</f>
+        <f t="shared" ref="C30:E31" si="0">3*25.4</f>
         <v>76.199999999999989</v>
       </c>
       <c r="D30" s="2">
-        <f>3*25.4</f>
+        <f t="shared" si="0"/>
         <v>76.199999999999989</v>
       </c>
       <c r="E30" s="2">
-        <f>3*25.4</f>
+        <f t="shared" si="0"/>
         <v>76.199999999999989</v>
       </c>
     </row>
@@ -1436,15 +1444,15 @@
         <v>26</v>
       </c>
       <c r="C31" s="2">
-        <f>3*25.4</f>
+        <f t="shared" si="0"/>
         <v>76.199999999999989</v>
       </c>
       <c r="D31" s="2">
-        <f>3*25.4</f>
+        <f t="shared" si="0"/>
         <v>76.199999999999989</v>
       </c>
       <c r="E31" s="2">
-        <f>3*25.4</f>
+        <f t="shared" si="0"/>
         <v>76.199999999999989</v>
       </c>
     </row>
@@ -1464,7 +1472,7 @@
         <v>176.5</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" ref="E32" si="0">AVERAGE(E34,D35)</f>
+        <f t="shared" ref="E32" si="1">AVERAGE(E34,D35)</f>
         <v>186</v>
       </c>
     </row>
@@ -1480,7 +1488,7 @@
         <v>176.5</v>
       </c>
       <c r="D33" s="2">
-        <f t="shared" ref="D33" si="1">E32</f>
+        <f t="shared" ref="D33" si="2">E32</f>
         <v>186</v>
       </c>
       <c r="E33" s="2">

--- a/data/gravel/Singular Gryphon steel 2025.xlsx
+++ b/data/gravel/Singular Gryphon steel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321CE043-3ECD-9640-B68D-880B1A1BDA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBD126C-DE4E-E84C-BADF-869CDC82C42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -320,9 +320,6 @@
     <t>seat_tube_ct</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>https://singularcycles.com/products/gryphon-steel?srsltid=AfmBOorB0zvEMixhf6ur3m7RauWmSXa4A9Ge7ueeIFRRq0lr_Ky_-wWG</t>
   </si>
   <si>
@@ -366,6 +363,15 @@
   </si>
   <si>
     <t>https://singularcycles.com/cdn/shop/files/edited_4.jpg?v=1753953935&amp;width=2200</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Watford, Hertfordshire, England</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -746,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V75"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -768,7 +774,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -792,12 +798,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -805,7 +811,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="22" x14ac:dyDescent="0.3">
@@ -813,7 +819,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>90</v>
@@ -943,7 +949,7 @@
         <v>94</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="9">
         <v>430</v>
@@ -975,7 +981,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13" s="9">
         <v>380</v>
@@ -1169,7 +1175,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C19" s="9">
         <v>811</v>
@@ -1526,13 +1532,13 @@
     </row>
     <row r="36" spans="1:12" ht="22" x14ac:dyDescent="0.3">
       <c r="C36" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="E36" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="F36" s="7"/>
       <c r="L36" s="1"/>
@@ -1545,13 +1551,13 @@
         <v>32</v>
       </c>
       <c r="C37" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="E37" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -1672,7 +1678,7 @@
         <v>47</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -1808,7 +1814,15 @@
         <v>67</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>95</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Singular Gryphon steel 2025.xlsx
+++ b/data/gravel/Singular Gryphon steel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBD126C-DE4E-E84C-BADF-869CDC82C42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7544A5-6AEE-3648-9050-02CE4B8B3020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -752,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V76"/>
+  <dimension ref="A1:V82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -1654,125 +1672,113 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="2">
-        <v>27.2</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B56" s="2">
-        <v>42</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B58" s="2">
-        <v>160</v>
+        <v>44</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="2">
-        <v>160</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B60" s="2">
+        <v>27.2</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B62" s="2">
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="B64" s="2">
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B65" s="2">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="2">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>74</v>
@@ -1780,48 +1786,90 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B71" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B72" s="2">
-        <v>1140</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" s="2">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B82" s="2" t="s">
         <v>111</v>
       </c>
     </row>
